--- a/tricount_extractor/tests/data/expected_results/foreign_currency_trip_6.xlsx
+++ b/tricount_extractor/tests/data/expected_results/foreign_currency_trip_6.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,45 +514,65 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>created</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>original_amount</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>original_currency</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>payer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>is_reimbursement</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>type_transaction</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
@@ -568,36 +588,54 @@
       <c r="C2" s="1" t="n">
         <v>45717.5</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="1" t="n">
+        <v>45717.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Sushi</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>18.52</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>-18.52</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>JPY</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="J2" t="b">
+      <c r="K2" t="b">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>FOOD</t>
         </is>
@@ -613,36 +651,54 @@
       <c r="C3" s="1" t="n">
         <v>45717.75</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="1" t="n">
+        <v>45717.75</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>Taxi</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="J3" t="b">
+      <c r="K3" t="b">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>TRANSPORT</t>
         </is>
@@ -659,7 +715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,27 +746,42 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>type_transaction</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>participant</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>original_share</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>original_currency</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>split_type</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>share_ratio</t>
         </is>
       </c>
     </row>
@@ -739,24 +810,37 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>9.26</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>-9.26</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>JPY</t>
         </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -784,24 +868,37 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>9.26</v>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>-9.26</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>1500</v>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>JPY</t>
         </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -829,24 +926,37 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -874,24 +984,37 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>10</v>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
